--- a/docs/data/jp/xlsx/4368.xlsx
+++ b/docs/data/jp/xlsx/4368.xlsx
@@ -2076,7 +2076,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Life Science Business Unit</t>
+          <t>생명과학 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Life Science Business Unit Reportable Segments</t>
+          <t>생명과학 사업</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -2874,7 +2874,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Electronic Materials And Functional Chemicals Business Unit</t>
+          <t>전자재료 및 기능성 화학품 사업</t>
         </is>
       </c>
       <c r="B16" s="10" t="n"/>
@@ -9998,7 +9998,7 @@
     <row r="125">
       <c r="A125" s="18" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Memberships EI</t>
+          <t>회원권 매각 이익</t>
         </is>
       </c>
       <c r="T125" s="20" t="n">
@@ -11857,7 +11857,7 @@
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>생명과학 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C157" s="20" t="n">
@@ -12265,7 +12265,7 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>생명과학 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C166" s="20" t="n">
@@ -12489,7 +12489,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>생명과학 사업 · 계</t>
         </is>
       </c>
       <c r="C171" s="20" t="n">
@@ -12897,7 +12897,7 @@
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>생명과학 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="C180" s="20" t="n">
@@ -13545,7 +13545,7 @@
     <row r="193">
       <c r="A193" s="18" t="inlineStr">
         <is>
-          <t>부문 · 감가상각비</t>
+          <t>생명과학 사업 · 감가상각비</t>
         </is>
       </c>
       <c r="E193" s="20" t="n">
@@ -14451,7 +14451,7 @@
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Directors Retirement Benefits Ope CF</t>
+          <t>임원 퇴직 공로 충당금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="O208" s="20" t="n">
@@ -14754,7 +14754,7 @@
     <row r="214">
       <c r="A214" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Investments In Capital Ope CF</t>
+          <t>출자금 평가손</t>
         </is>
       </c>
       <c r="H214" s="20" t="n">
@@ -15058,7 +15058,7 @@
     <row r="221">
       <c r="A221" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Sales Of Membership Ope CF</t>
+          <t>회원권 매각 손익(△는 이익)</t>
         </is>
       </c>
       <c r="S221" s="20" t="n">
@@ -22180,7 +22180,7 @@
     <row r="131">
       <c r="A131" s="18" t="inlineStr">
         <is>
-          <t>Long Term Accounts Payable Facilities</t>
+          <t>장기 설비 관련 미지급금</t>
         </is>
       </c>
       <c r="C131" s="20" t="n">
